--- a/docs/program/RKA MTs.xlsx
+++ b/docs/program/RKA MTs.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Download\Laporan Program Pesantren\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Download\Tugas Akhir\Smart_Santri\smart_santri\docs\program\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{357C802A-777B-43D4-94FF-9A7B935C53DD}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EB1E704-5490-4787-B0A5-BC0CC918A506}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C1FC1C74-BFAF-46C3-BEC8-D7E540D7ABE9}"/>
   </bookViews>
@@ -2154,12 +2154,6 @@
     <t>ISI</t>
   </si>
   <si>
-    <t>PENILAIAN</t>
-  </si>
-  <si>
-    <t>PROSES</t>
-  </si>
-  <si>
     <t>PENGEMBANGAN PENDIDIK DAN TENAGA KEPENDIDIKAN</t>
   </si>
   <si>
@@ -2170,6 +2164,12 @@
   </si>
   <si>
     <t>PENGEMBANGAN SARANA DAN PRASARANA</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN PENILAIAN</t>
+  </si>
+  <si>
+    <t>PENGEMBANGAN PROSES</t>
   </si>
 </sst>
 </file>
@@ -3574,7 +3574,7 @@
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="7" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>128</v>
@@ -3888,7 +3888,7 @@
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="7" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>164</v>
@@ -6338,7 +6338,7 @@
     </row>
     <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="7" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>431</v>
@@ -6834,7 +6834,7 @@
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" s="7" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="B222" s="6" t="s">
         <v>486</v>
@@ -7870,7 +7870,7 @@
     </row>
     <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="7" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>597</v>
@@ -8279,7 +8279,7 @@
     </row>
     <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="7" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B297" s="6" t="s">
         <v>641</v>
@@ -8738,6 +8738,34 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="B297:B301"/>
+    <mergeCell ref="B302:B305"/>
+    <mergeCell ref="A297:A319"/>
+    <mergeCell ref="A276:A296"/>
+    <mergeCell ref="B268:B273"/>
+    <mergeCell ref="B274:B275"/>
+    <mergeCell ref="B276:B287"/>
+    <mergeCell ref="A196:A221"/>
+    <mergeCell ref="A222:A275"/>
+    <mergeCell ref="B290:B296"/>
+    <mergeCell ref="B215:B221"/>
+    <mergeCell ref="B222:B239"/>
+    <mergeCell ref="B240:B242"/>
+    <mergeCell ref="B243:B255"/>
+    <mergeCell ref="B256:B264"/>
+    <mergeCell ref="B265:B267"/>
+    <mergeCell ref="B196:B214"/>
+    <mergeCell ref="B128:B131"/>
+    <mergeCell ref="B132:B170"/>
+    <mergeCell ref="B171:B185"/>
+    <mergeCell ref="B186:B195"/>
+    <mergeCell ref="A68:A195"/>
+    <mergeCell ref="B68:B83"/>
+    <mergeCell ref="B84:B89"/>
+    <mergeCell ref="B90:B105"/>
+    <mergeCell ref="B106:B111"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B115:B127"/>
     <mergeCell ref="B58:B65"/>
     <mergeCell ref="A52:A67"/>
     <mergeCell ref="B3:B5"/>
@@ -8750,34 +8778,6 @@
     <mergeCell ref="B49:B51"/>
     <mergeCell ref="A15:A51"/>
     <mergeCell ref="B52:B57"/>
-    <mergeCell ref="B128:B131"/>
-    <mergeCell ref="B132:B170"/>
-    <mergeCell ref="B171:B185"/>
-    <mergeCell ref="B186:B195"/>
-    <mergeCell ref="A68:A195"/>
-    <mergeCell ref="B68:B83"/>
-    <mergeCell ref="B84:B89"/>
-    <mergeCell ref="B90:B105"/>
-    <mergeCell ref="B106:B111"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B115:B127"/>
-    <mergeCell ref="A196:A221"/>
-    <mergeCell ref="A222:A275"/>
-    <mergeCell ref="B290:B296"/>
-    <mergeCell ref="B215:B221"/>
-    <mergeCell ref="B222:B239"/>
-    <mergeCell ref="B240:B242"/>
-    <mergeCell ref="B243:B255"/>
-    <mergeCell ref="B256:B264"/>
-    <mergeCell ref="B265:B267"/>
-    <mergeCell ref="B196:B214"/>
-    <mergeCell ref="B297:B301"/>
-    <mergeCell ref="B302:B305"/>
-    <mergeCell ref="A297:A319"/>
-    <mergeCell ref="A276:A296"/>
-    <mergeCell ref="B268:B273"/>
-    <mergeCell ref="B274:B275"/>
-    <mergeCell ref="B276:B287"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
